--- a/results/mcdm/promethee_phi.xlsx
+++ b/results/mcdm/promethee_phi.xlsx
@@ -470,26 +470,26 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.2046461440958391</v>
+        <v>0.1403550084224461</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1590855189970676</v>
+        <v>0.3041565527061872</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2684428027980809</v>
+        <v>-0.1125258517159711</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1504312013949457</v>
+        <v>0.5999578478934631</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1494084429547</v>
+        <v>0.6921593393936961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1657923307475354</v>
+        <v>0.4375092300985494</v>
       </c>
     </row>
     <row r="3">
@@ -499,26 +499,26 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1773943483888261</v>
+        <v>0.6716849825488848</v>
       </c>
       <c r="E3" t="n">
-        <v>0.138249477466679</v>
+        <v>0.7282427022764747</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2234162402797157</v>
+        <v>0.5618881644524459</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7766257642567348</v>
+        <v>0.999999999999247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.778212417406139</v>
+        <v>0.999999999999274</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7527953236428612</v>
+        <v>0.9619197706737632</v>
       </c>
     </row>
     <row r="4">
@@ -528,26 +528,26 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1543365451116594</v>
+        <v>0.16678216756741</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1191919239586663</v>
+        <v>0.3257598141374103</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2233283518123611</v>
+        <v>-0.09096434601798559</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2328926104952255</v>
+        <v>0.6198550457426431</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2337754075355462</v>
+        <v>0.707840969828836</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2196336052430382</v>
+        <v>0.4542750157845227</v>
       </c>
     </row>
     <row r="5">
@@ -557,26 +557,26 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.08892894228929188</v>
+        <v>0.5677823413873742</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0680997812436515</v>
+        <v>0.6433059934878418</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1440860864324499</v>
+        <v>0.4771156250678417</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6316239715394038</v>
+        <v>0.9217709555188116</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6298598577807568</v>
+        <v>0.9383451391422283</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6581197486167328</v>
+        <v>0.8960023784801937</v>
       </c>
     </row>
     <row r="6">
@@ -586,26 +586,26 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01310098386680217</v>
+        <v>0.4400302945647122</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01145227288402219</v>
+        <v>0.5441166198456836</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01656158591754892</v>
+        <v>0.2497336958442445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5073359544021137</v>
+        <v>0.8255855222936668</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5100617215944936</v>
+        <v>0.8663443856679753</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4663968031951486</v>
+        <v>0.7191948425119552</v>
       </c>
     </row>
     <row r="7">
@@ -615,26 +615,26 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.2281132886979949</v>
+        <v>0.1573356453443884</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1755666867598104</v>
+        <v>0.3184261910194245</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3461060778981737</v>
+        <v>-0.1077980066273381</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1119666965981114</v>
+        <v>0.6127426913413583</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1145540735865885</v>
+        <v>0.7025175529062118</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0731060712115959</v>
+        <v>0.4411855057085551</v>
       </c>
     </row>
     <row r="8">
@@ -644,26 +644,26 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07929088924690811</v>
+        <v>0.5591035027267626</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06045717242157764</v>
+        <v>0.6362113519686332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1354432930022116</v>
+        <v>0.4700346963835972</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6158264408314345</v>
+        <v>0.9152365955831088</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6136972705991177</v>
+        <v>0.9331951970037125</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6478051154267449</v>
+        <v>0.8904963932099351</v>
       </c>
     </row>
     <row r="9">
@@ -673,26 +673,26 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06564628904318211</v>
+        <v>-0.5393367896078776</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04886393027776749</v>
+        <v>-0.5608043764907195</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1437965668030936</v>
+        <v>-0.5683019124398562</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3782629500833242</v>
+        <v>0.08821301343397098</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3825050305792192</v>
+        <v>0.06429128920674024</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3145498144452007</v>
+        <v>0.08310709038120612</v>
       </c>
     </row>
     <row r="10">
@@ -702,26 +702,26 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2069823160854652</v>
+        <v>-0.6231808145388128</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1588106306354732</v>
+        <v>-0.6289553084996403</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3271571646200468</v>
+        <v>-0.645835331572374</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1466020308578133</v>
+        <v>0.02508624512068799</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1499897767914725</v>
+        <v>0.01482108615537914</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09572041359874014</v>
+        <v>0.02281868998447605</v>
       </c>
     </row>
     <row r="11">
@@ -731,26 +731,26 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1498228536305858</v>
+        <v>-0.5581506798782012</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1134853548664352</v>
+        <v>-0.5757954893804316</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2759001914109852</v>
+        <v>-0.5927782620881294</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2402909075854149</v>
+        <v>0.07404790037857364</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2458436583918297</v>
+        <v>0.05340936321161432</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1568924040377077</v>
+        <v>0.06407478167670617</v>
       </c>
     </row>
     <row r="12">
@@ -760,26 +760,26 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1792405158351384</v>
+        <v>-0.1238347881884533</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1397134179067413</v>
+        <v>-0.2314034695419425</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2250717659139844</v>
+        <v>0.01160987290575538</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7796517786184444</v>
+        <v>0.4010474533229817</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7813083582742488</v>
+        <v>0.303400708134796</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7547710899031492</v>
+        <v>0.5340346297683555</v>
       </c>
     </row>
     <row r="13">
@@ -789,26 +789,26 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05143705597459605</v>
+        <v>-0.3117257060434891</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04185131733898198</v>
+        <v>-0.3797542284833813</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01781576713263031</v>
+        <v>-0.2648384203307914</v>
       </c>
       <c r="G13" t="n">
-        <v>0.57017180658954</v>
+        <v>0.2595830323415803</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5743496130305605</v>
+        <v>0.1957141079472029</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5074240231116536</v>
+        <v>0.3190740930332031</v>
       </c>
     </row>
     <row r="14">
@@ -818,26 +818,26 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3136746805608447</v>
+        <v>0.09773294394859711</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2431235125634666</v>
+        <v>-0.0559436756643884</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4305529278748904</v>
+        <v>0.3254122681240288</v>
       </c>
       <c r="G14" t="n">
-        <v>0.999999999998361</v>
+        <v>0.5678673895538163</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9999999999978852</v>
+        <v>0.4307655346251565</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9999999999988066</v>
+        <v>0.7780409519458543</v>
       </c>
     </row>
     <row r="15">
@@ -847,26 +847,26 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.3121770953250033</v>
+        <v>0.09646181606550353</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2419359845342144</v>
+        <v>-0.05698277743920854</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4292099886131295</v>
+        <v>0.3243751747707913</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9975453394308202</v>
+        <v>0.5669103482448059</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9974886160254397</v>
+        <v>0.4300112591622083</v>
       </c>
       <c r="I15" t="n">
-        <v>0.99839728601596</v>
+        <v>0.7772345293731323</v>
       </c>
     </row>
     <row r="16">
@@ -876,26 +876,26 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.165072078680131</v>
+        <v>-0.1411223285602159</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1284783871054295</v>
+        <v>-0.2455354181220143</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2123664119362111</v>
+        <v>-0.002494760822949638</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7564285902778245</v>
+        <v>0.3880315400643598</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7575485180100013</v>
+        <v>0.2931424424712238</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7396080448891169</v>
+        <v>0.5230671551593484</v>
       </c>
     </row>
     <row r="17">
@@ -905,26 +905,26 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.1924643998235335</v>
+        <v>-0.1101791536607554</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1501994540374154</v>
+        <v>-0.220240474643669</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2369301046422039</v>
+        <v>0.02275129147683452</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8013267696634852</v>
+        <v>0.4113288785970062</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8034842248006542</v>
+        <v>0.3115038346511965</v>
       </c>
       <c r="I17" t="n">
-        <v>0.768923275213546</v>
+        <v>0.5426979688976764</v>
       </c>
     </row>
     <row r="18">
@@ -934,26 +934,26 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.1354504853690618</v>
+        <v>-0.03709190560611514</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1020886144680808</v>
+        <v>0.04573940181057545</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2630119649775538</v>
+        <v>-0.2301227481132733</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2638483551279026</v>
+        <v>0.4663567923738222</v>
       </c>
       <c r="H18" t="n">
-        <v>0.269945482070531</v>
+        <v>0.504576447275849</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1722736958854623</v>
+        <v>0.3460682894727301</v>
       </c>
     </row>
     <row r="19">
@@ -963,26 +963,26 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.05708460704675546</v>
+        <v>0.06921258291708632</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.04420222641574043</v>
+        <v>0.1272371561789928</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.07949956326396279</v>
+        <v>-0.01650501816053962</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3922962235728595</v>
+        <v>0.5463942049764967</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3923636007139852</v>
+        <v>0.5637349993013417</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3912842651843762</v>
+        <v>0.5121730657011473</v>
       </c>
     </row>
     <row r="20">
@@ -992,26 +992,26 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.0647537786049634</v>
+        <v>-0.03447773748507205</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.04815620350775211</v>
+        <v>0.04748781877582731</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1429962201648323</v>
+        <v>-0.2188634983247122</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3797258452337182</v>
+        <v>0.4683250183200955</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3840017309713832</v>
+        <v>0.5058456088227247</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3155049780812565</v>
+        <v>0.3548232517459581</v>
       </c>
     </row>
     <row r="21">
@@ -1021,26 +1021,26 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1728319203499893</v>
+        <v>0.3720800288032374</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1346316458749296</v>
+        <v>0.3695771320425179</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2193249447756767</v>
+        <v>0.3537508255084533</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7691475840963362</v>
+        <v>0.7744252793653962</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7705614280814923</v>
+        <v>0.7396476018151451</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7479126184461404</v>
+        <v>0.8000764343658646</v>
       </c>
     </row>
     <row r="22">
@@ -1050,26 +1050,26 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.1816834256084698</v>
+        <v>-0.0933630408124102</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1387495744555682</v>
+        <v>-0.0002602471953956353</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3044707274895024</v>
+        <v>-0.2760334869757913</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1880689119208626</v>
+        <v>0.4239898506887197</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1924148932683212</v>
+        <v>0.4711856790275314</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1227952568514541</v>
+        <v>0.3103690382592318</v>
       </c>
     </row>
     <row r="23">
@@ -1079,26 +1079,26 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1461460399753662</v>
+        <v>0.3400029140136692</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1134707595549411</v>
+        <v>0.3433552330878417</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1953947432538897</v>
+        <v>0.3275796093926259</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7254073169663018</v>
+        <v>0.7502741893485745</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7258103911057753</v>
+        <v>0.7206133402512636</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7193534202132934</v>
+        <v>0.7797262321728775</v>
       </c>
     </row>
     <row r="24">
@@ -1108,26 +1108,26 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.1660535953136879</v>
+        <v>-0.07347220708147489</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1263557145781511</v>
+        <v>0.01599980099280573</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2904548890215634</v>
+        <v>-0.2598048669234172</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2136874391230224</v>
+        <v>0.4389658022073293</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2186254249662417</v>
+        <v>0.4829887147569613</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1395222831090894</v>
+        <v>0.3229880811771211</v>
       </c>
     </row>
     <row r="25">
@@ -1137,26 +1137,26 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1604799835888563</v>
+        <v>0.4442174055847122</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1216459550708512</v>
+        <v>0.4228829321896402</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2931776597876161</v>
+        <v>0.5456353316044964</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7489017834736582</v>
+        <v>0.8287380282412196</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7430992924912825</v>
+        <v>0.7783418453032347</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8360512129389474</v>
+        <v>0.9492819003814242</v>
       </c>
     </row>
     <row r="26">
@@ -1166,26 +1166,26 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1534008224424589</v>
+        <v>0.4403888406478417</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1160324500203584</v>
+        <v>0.4197532167032375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2868295179815249</v>
+        <v>0.5425116653697482</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7372984788326603</v>
+        <v>0.8258554742137707</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7312278534466577</v>
+        <v>0.7760700104795366</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8284751028888369</v>
+        <v>0.9468530014269698</v>
       </c>
     </row>
     <row r="27">
@@ -1195,26 +1195,26 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.01085019507623672</v>
+        <v>-0.2426970565361151</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0110212727840924</v>
+        <v>-0.3109893544352519</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05461049742030014</v>
+        <v>-0.09104030589359718</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4680780790635126</v>
+        <v>0.3115551981341966</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4625346729651897</v>
+        <v>0.2456299664935972</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5513362315087701</v>
+        <v>0.4542159509393733</v>
       </c>
     </row>
     <row r="28">
@@ -1224,26 +1224,26 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.01554509715331406</v>
+        <v>-0.2356164132674101</v>
       </c>
       <c r="E28" t="n">
-        <v>0.009909188209188111</v>
+        <v>-0.305201180731223</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07828011796166595</v>
+        <v>-0.08526331982611512</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5113420492562957</v>
+        <v>0.3168862652853828</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5067984065189367</v>
+        <v>0.2498315543515208</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5795844426457173</v>
+        <v>0.458708017109284</v>
       </c>
     </row>
     <row r="29">
@@ -1253,26 +1253,26 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.07072245653096963</v>
+        <v>-0.2024724952319785</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05366273176243169</v>
+        <v>-0.2781072081158993</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1277596671019297</v>
+        <v>-0.05822171563194251</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6017821023790566</v>
+        <v>0.3418405591249331</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5993283892314435</v>
+        <v>0.2694988470390607</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6386351886698221</v>
+        <v>0.4797350152639987</v>
       </c>
     </row>
     <row r="30">
@@ -1282,26 +1282,26 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.04060627977078111</v>
+        <v>-0.3443937652722662</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0311355407626768</v>
+        <v>-0.3897704051041008</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.06472284662878613</v>
+        <v>-0.2762374769116546</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4193055043906158</v>
+        <v>0.2349870160139012</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4199970241901074</v>
+        <v>0.188443447420353</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4089193519273944</v>
+        <v>0.3102104198587044</v>
       </c>
     </row>
     <row r="31">
@@ -1311,26 +1311,26 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.09690447578593572</v>
+        <v>-0.3860936849359352</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.07577786506200927</v>
+        <v>-0.4238586043393525</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1152074908317506</v>
+        <v>-0.3102597889771224</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3270283114304164</v>
+        <v>0.2035908471222084</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3255874481831574</v>
+        <v>0.1636991029467893</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3486690878335236</v>
+        <v>0.2837553660873796</v>
       </c>
     </row>
     <row r="32">
@@ -1340,26 +1340,26 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.2888220781622149</v>
+        <v>-0.6298089707837771</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2237064436065851</v>
+        <v>-0.6167938038246763</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4005458619947869</v>
+        <v>-0.6569154541906476</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01246019237083628</v>
+        <v>0.02009585869822368</v>
       </c>
       <c r="H32" t="n">
-        <v>0.01274812812308954</v>
+        <v>0.02364902273593529</v>
       </c>
       <c r="I32" t="n">
-        <v>0.008135595122915285</v>
+        <v>0.01420301333395187</v>
       </c>
     </row>
     <row r="33">
@@ -1369,26 +1369,26 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.1181484684229821</v>
+        <v>0.01318352646643883</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.09262354175936499</v>
+        <v>0.05675924437453245</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1342577532849734</v>
+        <v>-0.03344673178924457</v>
       </c>
       <c r="G33" t="n">
-        <v>0.292207728417666</v>
+        <v>0.5042095261244812</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2899622154133821</v>
+        <v>0.5125756606858963</v>
       </c>
       <c r="I33" t="n">
-        <v>0.325933791547196</v>
+        <v>0.498999535808078</v>
       </c>
     </row>
     <row r="34">
@@ -1398,26 +1398,26 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.2283411310888156</v>
+        <v>-0.1884504285921942</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1757473570942099</v>
+        <v>-0.1017759658638848</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3463103924739345</v>
+        <v>-0.3457688975670862</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1115932449113716</v>
+        <v>0.3523978737668794</v>
       </c>
       <c r="H34" t="n">
-        <v>0.114171992009623</v>
+        <v>0.3974962507629607</v>
       </c>
       <c r="I34" t="n">
-        <v>0.07286223454913812</v>
+        <v>0.2561442097582135</v>
       </c>
     </row>
     <row r="35">
@@ -1427,26 +1427,26 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.1910695041234207</v>
+        <v>0.4137649596241727</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1459022792965426</v>
+        <v>0.3742039765668345</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3206083977123456</v>
+        <v>0.528634558840899</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7990404253613692</v>
+        <v>0.805810163049785</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7943965607580443</v>
+        <v>0.7430061903385574</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8687880823444302</v>
+        <v>0.9360624473134025</v>
       </c>
     </row>
     <row r="36">
@@ -1456,26 +1456,26 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.2823470681888053</v>
+        <v>0.5145468681977339</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2182819096343087</v>
+        <v>0.4565895976057553</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4024603160991052</v>
+        <v>0.6108609413303236</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9486515672517976</v>
+        <v>0.8816895855600266</v>
       </c>
       <c r="H36" t="n">
-        <v>0.94746498447877</v>
+        <v>0.8028092375041401</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9664732255647251</v>
+        <v>0.9999999999992224</v>
       </c>
     </row>
     <row r="37">
@@ -1485,26 +1485,26 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2557707822419178</v>
+        <v>0.4830409199284893</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1972079275196177</v>
+        <v>0.430834606940072</v>
       </c>
       <c r="F37" t="n">
-        <v>0.378628391894932</v>
+        <v>0.5851557310426259</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9050909340509358</v>
+        <v>0.8579685309169418</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9028977324941827</v>
+        <v>0.7841139008409455</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9380313151613587</v>
+        <v>0.980012154403788</v>
       </c>
     </row>
     <row r="38">
@@ -1514,26 +1514,26 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.04929291821855539</v>
+        <v>0.02403439071517982</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.03802371406315347</v>
+        <v>0.06652042744266196</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.07251247191691487</v>
+        <v>-0.04552029690068349</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4050674174010259</v>
+        <v>0.5123792197191458</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4054299170565275</v>
+        <v>0.5196612234825823</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3996229215333283</v>
+        <v>0.4896113786005347</v>
       </c>
     </row>
     <row r="39">
@@ -1543,26 +1543,26 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1257486766846971</v>
+        <v>0.264329833599892</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09729642766998636</v>
+        <v>0.2577100192751079</v>
       </c>
       <c r="F39" t="n">
-        <v>0.177103684191698</v>
+        <v>0.2736840284477338</v>
       </c>
       <c r="G39" t="n">
-        <v>0.691974426368072</v>
+        <v>0.6932993838240556</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6916049181735089</v>
+        <v>0.6584441814033909</v>
       </c>
       <c r="I39" t="n">
-        <v>0.697524185671735</v>
+        <v>0.7378181311246513</v>
       </c>
     </row>
     <row r="40">
@@ -1572,26 +1572,26 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.09404963501867351</v>
+        <v>0.2271261858847842</v>
       </c>
       <c r="E40" t="n">
-        <v>0.07216029546333895</v>
+        <v>0.2272973622287771</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1486779982309371</v>
+        <v>0.2433301543216906</v>
       </c>
       <c r="G40" t="n">
-        <v>0.640017191651676</v>
+        <v>0.6652884903625933</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6384470322137111</v>
+        <v>0.6363678828838569</v>
       </c>
       <c r="I40" t="n">
-        <v>0.663599908037929</v>
+        <v>0.7142155796393997</v>
       </c>
     </row>
     <row r="41">
@@ -1601,26 +1601,26 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.01478975254549217</v>
+        <v>0.173093342570036</v>
       </c>
       <c r="E41" t="n">
-        <v>0.009310228716222113</v>
+        <v>0.1831274371302159</v>
       </c>
       <c r="F41" t="n">
-        <v>0.07760277292264814</v>
+        <v>0.1992456027957914</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5101039797432216</v>
+        <v>0.6246067747120422</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5055317271364499</v>
+        <v>0.6043052962254205</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5787760737222992</v>
+        <v>0.6799363343353706</v>
       </c>
     </row>
     <row r="42">
@@ -1630,26 +1630,26 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-0.1591142237186509</v>
+        <v>-0.116843350976187</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1208530573154597</v>
+        <v>-0.04323973010812954</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.2842321016009273</v>
+        <v>-0.2873458032206834</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2250616176406677</v>
+        <v>0.4063113565938367</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2302624431375834</v>
+        <v>0.4399872245961652</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1469487905434296</v>
+        <v>0.3015728125952917</v>
       </c>
     </row>
     <row r="43">
@@ -1659,26 +1659,26 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2754218395110786</v>
+        <v>0.506362600533705</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2127904671661542</v>
+        <v>0.4498992502627338</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3962502111478722</v>
+        <v>0.6041835253847122</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9373005700934506</v>
+        <v>0.8755275916783325</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9358516833520459</v>
+        <v>0.7979527691949452</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9590618538640909</v>
+        <v>0.994807777978722</v>
       </c>
     </row>
     <row r="44">
@@ -1688,26 +1688,26 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-0.0593020701119879</v>
+        <v>-0.002661129827625952</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.04383320640029019</v>
+        <v>0.04761161250007195</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.1381074744669762</v>
+        <v>-0.1357376374414029</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3886616263453126</v>
+        <v>0.4922799706468794</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3931440041482495</v>
+        <v>0.5059354696726697</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3213393901888159</v>
+        <v>0.4194602204276859</v>
       </c>
     </row>
     <row r="45">
@@ -1717,26 +1717,26 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2031988237141892</v>
+        <v>0.4238263397842447</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1555203675662906</v>
+        <v>0.3824287965243885</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3314852006528726</v>
+        <v>0.5368434815049279</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8189213388466251</v>
+        <v>0.8133854484061347</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8147368913702187</v>
+        <v>0.7489765197437052</v>
       </c>
       <c r="I45" t="n">
-        <v>0.881768866105708</v>
+        <v>0.9424455376237741</v>
       </c>
     </row>
     <row r="46">
@@ -1746,26 +1746,26 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.2591435978023621</v>
+        <v>-0.2082138841725898</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.200172539525906</v>
+        <v>-0.1179318869504316</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3739320869983639</v>
+        <v>-0.3618935917792446</v>
       </c>
       <c r="G46" t="n">
-        <v>0.06110556740548961</v>
+        <v>0.3375178261722991</v>
       </c>
       <c r="H46" t="n">
-        <v>0.062517622452003</v>
+        <v>0.3857688000433049</v>
       </c>
       <c r="I46" t="n">
-        <v>0.03989747038983421</v>
+        <v>0.2436059774473708</v>
       </c>
     </row>
     <row r="47">
@@ -1775,26 +1775,26 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.08818884308436103</v>
+        <v>-0.111416223251187</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.06886670042304237</v>
+        <v>-0.04129180319884895</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1073918653395186</v>
+        <v>-0.2244692167108273</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3413139222936302</v>
+        <v>0.4103974800210562</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3402031773934944</v>
+        <v>0.441401208776436</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3579965478443861</v>
+        <v>0.3504643598209704</v>
       </c>
     </row>
     <row r="48">
@@ -1804,26 +1804,26 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2792789015599711</v>
+        <v>0.5109581222364028</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2158489704045699</v>
+        <v>0.4536559255910073</v>
       </c>
       <c r="F48" t="n">
-        <v>0.399708979261058</v>
+        <v>0.6079329396457912</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9436225996456817</v>
+        <v>0.8789875929609977</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9423198052181607</v>
+        <v>0.8006797090299486</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9631896771962927</v>
+        <v>0.9977232457957519</v>
       </c>
     </row>
     <row r="49">
@@ -1833,26 +1833,26 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.04275801757420958</v>
+        <v>0.1300529104594244</v>
       </c>
       <c r="E49" t="n">
-        <v>0.03496917058649784</v>
+        <v>0.1531867916183454</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01003295708398452</v>
+        <v>0.04097855471701439</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5559461766783105</v>
+        <v>0.5922013243750833</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5597952508391333</v>
+        <v>0.5825716270106375</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4981357262794893</v>
+        <v>0.5568711158664998</v>
       </c>
     </row>
     <row r="50">
@@ -1862,26 +1862,26 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.1714141924516648</v>
+        <v>0.3186963699191367</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1335074416715094</v>
+        <v>0.3021527265207914</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2180536164989365</v>
+        <v>0.3180408348754316</v>
       </c>
       <c r="G50" t="n">
-        <v>0.766823816016742</v>
+        <v>0.7342323393333798</v>
       </c>
       <c r="H50" t="n">
-        <v>0.7681839613197153</v>
+        <v>0.6907047783869855</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7463953676933045</v>
+        <v>0.7723090762700295</v>
       </c>
     </row>
     <row r="51">
@@ -1891,26 +1891,26 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.1203769428213222</v>
+        <v>0.3750773635173382</v>
       </c>
       <c r="E51" t="n">
-        <v>0.08984577179585451</v>
+        <v>0.3425782445592086</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2572158015415553</v>
+        <v>0.4970699544381654</v>
       </c>
       <c r="G51" t="n">
-        <v>0.68316972999542</v>
+        <v>0.7766819941904568</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6758482730370683</v>
+        <v>0.7200493306457159</v>
       </c>
       <c r="I51" t="n">
-        <v>0.7931329852117075</v>
+        <v>0.9115184567363342</v>
       </c>
     </row>
     <row r="52">
@@ -1920,26 +1920,26 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-0.01085019507623672</v>
+        <v>0.1663315448610432</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0110212727840924</v>
+        <v>0.1775999083159713</v>
       </c>
       <c r="F52" t="n">
-        <v>0.05461049742030014</v>
+        <v>0.1937287578321942</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4680780790635126</v>
+        <v>0.6195157686718565</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4625346729651897</v>
+        <v>0.6002929083570179</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5513362315087701</v>
+        <v>0.6756465485653976</v>
       </c>
     </row>
     <row r="53">
@@ -1949,26 +1949,26 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.1500963235900682</v>
+        <v>0.308561593178669</v>
       </c>
       <c r="E53" t="n">
-        <v>0.11341210834235</v>
+        <v>0.2620866313718705</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2838662534252833</v>
+        <v>0.4508518733961151</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7318821440329319</v>
+        <v>0.7266017931647131</v>
       </c>
       <c r="H53" t="n">
-        <v>0.7256863555363929</v>
+        <v>0.6616211282582856</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8249386320487971</v>
+        <v>0.8755802225322012</v>
       </c>
     </row>
     <row r="54">
@@ -1978,26 +1978,26 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.03940161509410103</v>
+        <v>0.106432393411223</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0288264979268702</v>
+        <v>0.1025171454277698</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0996731270704847</v>
+        <v>0.1529090726256834</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5504447677303987</v>
+        <v>0.5744172675103274</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5468047282700922</v>
+        <v>0.5457909460764385</v>
       </c>
       <c r="I54" t="n">
-        <v>0.605115660482709</v>
+        <v>0.643905996512709</v>
       </c>
     </row>
     <row r="55">
@@ -2007,26 +2007,26 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-0.02472299160424712</v>
+        <v>0.002636207190179762</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.01854069845051305</v>
+        <v>0.02201984668525181</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.05047972324975683</v>
+        <v>-0.03400102922633091</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4453394690773559</v>
+        <v>0.4962683737188437</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4466325934896108</v>
+        <v>0.4873586165910961</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4259176285054773</v>
+        <v>0.4985685254618319</v>
       </c>
     </row>
     <row r="56">
@@ -2036,26 +2036,26 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.04692863082976086</v>
+        <v>0.1108630866486331</v>
       </c>
       <c r="E56" t="n">
-        <v>0.03479513460196101</v>
+        <v>0.1061390793558273</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1064228764092133</v>
+        <v>0.1565240059206475</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5627821414406854</v>
+        <v>0.5777531682581222</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5594271995835601</v>
+        <v>0.5484200782332249</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6131710639949309</v>
+        <v>0.6467168946819459</v>
       </c>
     </row>
     <row r="57">
@@ -2065,26 +2065,26 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-0.163508687587199</v>
+        <v>-0.2005401829517267</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1243376997201402</v>
+        <v>-0.1377762493018705</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2881727775118698</v>
+        <v>-0.347581643657482</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2178587440309079</v>
+        <v>0.3432954109134159</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2228931222716748</v>
+        <v>0.3713639400360791</v>
       </c>
       <c r="I57" t="n">
-        <v>0.142245840406986</v>
+        <v>0.2547346554868019</v>
       </c>
     </row>
     <row r="58">
@@ -2094,26 +2094,26 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.1242404676458069</v>
+        <v>0.1839917598527698</v>
       </c>
       <c r="E58" t="n">
-        <v>0.09610047536971739</v>
+        <v>0.1659191653151799</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1757512181785496</v>
+        <v>0.2161885463023021</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6895023525476511</v>
+        <v>0.6328122713273983</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6890757185548723</v>
+        <v>0.5918139527359226</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6959101021071846</v>
+        <v>0.6931108205562587</v>
       </c>
     </row>
     <row r="59">
@@ -2123,26 +2123,26 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.2177715959726273</v>
+        <v>0.3592681380578058</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1670760206981668</v>
+        <v>0.303537425961223</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3445531366542327</v>
+        <v>0.4922225500677698</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8428072643795665</v>
+        <v>0.7647791148425435</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8391747836571158</v>
+        <v>0.6917099203632433</v>
       </c>
       <c r="I59" t="n">
-        <v>0.897364630078578</v>
+        <v>0.907749214274993</v>
       </c>
     </row>
     <row r="60">
@@ -2152,26 +2152,26 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-0.06656153925517479</v>
+        <v>0.2951435497296044</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.04958968882192781</v>
+        <v>0.4137677657751798</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1446173050252686</v>
+        <v>0.06779988923913677</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3767627826464107</v>
+        <v>0.716499251919533</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3809701965957069</v>
+        <v>0.771725220701369</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3135703147296205</v>
+        <v>0.5777268368309088</v>
       </c>
     </row>
     <row r="61">
@@ -2181,26 +2181,26 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.04716842026580287</v>
+        <v>0.4421912293225899</v>
       </c>
       <c r="E61" t="n">
-        <v>0.03846645187053326</v>
+        <v>0.5310601845516546</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01398792591845563</v>
+        <v>0.2562106734599282</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5631751752788124</v>
+        <v>0.8272125055869072</v>
       </c>
       <c r="H61" t="n">
-        <v>0.567191300403868</v>
+        <v>0.8568668262849573</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5028557341258736</v>
+        <v>0.7242312077880381</v>
       </c>
     </row>
     <row r="62">
@@ -2210,26 +2210,26 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-0.003545695125503928</v>
+        <v>0.4141915920283453</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.001747909265355618</v>
+        <v>0.5072804902506475</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.03148926967248331</v>
+        <v>0.2542928229331655</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4800507318151229</v>
+        <v>0.8061313776498157</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4821459797621198</v>
+        <v>0.8396053410654136</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4485815466405275</v>
+        <v>0.7227399264573265</v>
       </c>
     </row>
     <row r="63">
@@ -2239,26 +2239,26 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1624984706274293</v>
+        <v>0.6145777639522663</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1264376139823057</v>
+        <v>0.6667366623753238</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2100585637979944</v>
+        <v>0.5200091829863311</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7522102432668625</v>
+        <v>0.957003565127063</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7532326915313301</v>
+        <v>0.9553532696743422</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7368537725353873</v>
+        <v>0.9293555315226298</v>
       </c>
     </row>
     <row r="64">
@@ -2268,26 +2268,26 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-0.02781716404258944</v>
+        <v>-0.143578471782554</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.02099425929628777</v>
+        <v>-0.1379757243116547</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.05325438044499414</v>
+        <v>-0.1611061978950719</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4402678758940115</v>
+        <v>0.3861822921988322</v>
       </c>
       <c r="H64" t="n">
-        <v>0.4414438036406847</v>
+        <v>0.3712191427611658</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4226062487498646</v>
+        <v>0.3997341468553932</v>
       </c>
     </row>
     <row r="65">
@@ -2297,26 +2297,26 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-0.1067235373348742</v>
+        <v>-0.3255578020384893</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.08143662299901014</v>
+        <v>-0.2817235391064029</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.180632032441898</v>
+        <v>-0.4273394563807553</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3109340934736711</v>
+        <v>0.2491687479619513</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3136203083457228</v>
+        <v>0.2668737820087289</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2705889909552662</v>
+        <v>0.1927166121446192</v>
       </c>
     </row>
     <row r="66">
@@ -2326,26 +2326,26 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.02042704039915046</v>
+        <v>-0.01318549296438842</v>
       </c>
       <c r="E66" t="n">
-        <v>0.01378038318554044</v>
+        <v>-0.03662748281661871</v>
       </c>
       <c r="F66" t="n">
-        <v>0.08265793439682792</v>
+        <v>0.06843042642672653</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5193439400947787</v>
+        <v>0.4843561020834782</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5149852086645214</v>
+        <v>0.4447870007179949</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5848090926464696</v>
+        <v>0.5782171296472937</v>
       </c>
     </row>
     <row r="67">
@@ -2355,26 +2355,26 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.04726758609135054</v>
+        <v>0.0008933215598920241</v>
       </c>
       <c r="E67" t="n">
-        <v>0.03506391320912591</v>
+        <v>-0.02511855334215829</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1067268299457967</v>
+        <v>0.07991711093643883</v>
       </c>
       <c r="G67" t="n">
-        <v>0.563337715904744</v>
+        <v>0.4949561426150726</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5599956125132283</v>
+        <v>0.4531412383083308</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6135338135228428</v>
+        <v>0.5871489405064128</v>
       </c>
     </row>
     <row r="68">
@@ -2384,26 +2384,26 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-0.1848066374120816</v>
+        <v>-0.3373310160160072</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.1412261624115093</v>
+        <v>-0.2909591498715108</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3072714253419416</v>
+        <v>-0.4460714283919064</v>
       </c>
       <c r="G68" t="n">
-        <v>0.1829497209226309</v>
+        <v>0.2403046106346501</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1871774056927065</v>
+        <v>0.2601697278397644</v>
       </c>
       <c r="I68" t="n">
-        <v>0.119452799200803</v>
+        <v>0.1781510139617451</v>
       </c>
     </row>
     <row r="69">
@@ -2413,26 +2413,26 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.1095195603194468</v>
+        <v>0.1849056683456835</v>
       </c>
       <c r="E69" t="n">
-        <v>0.08123628117274212</v>
+        <v>0.1196410504982013</v>
       </c>
       <c r="F69" t="n">
-        <v>0.24747959094548</v>
+        <v>0.3630786547942086</v>
       </c>
       <c r="G69" t="n">
-        <v>0.6653736219301002</v>
+        <v>0.6335003595929511</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6576409244699597</v>
+        <v>0.5582210484374098</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7815134270480664</v>
+        <v>0.8073295635726495</v>
       </c>
     </row>
     <row r="70">
@@ -2442,26 +2442,26 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-0.2724871461406808</v>
+        <v>-0.4031639056633093</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.2107534649264764</v>
+        <v>-0.3447751926032375</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.3858977331104301</v>
+        <v>-0.4997834531108273</v>
       </c>
       <c r="G70" t="n">
-        <v>0.03923443703290479</v>
+        <v>0.1907385553840531</v>
       </c>
       <c r="H70" t="n">
-        <v>0.04014108412189735</v>
+        <v>0.2211051034409263</v>
       </c>
       <c r="I70" t="n">
-        <v>0.02561722043090797</v>
+        <v>0.1363856424793046</v>
       </c>
     </row>
     <row r="71">
@@ -2471,26 +2471,26 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.1646123574150424</v>
+        <v>0.1482521281730576</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1281138456590595</v>
+        <v>0.1034739432871223</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2119541631228691</v>
+        <v>0.1976913979633814</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7556750707889394</v>
+        <v>0.6059036460496197</v>
       </c>
       <c r="H71" t="n">
-        <v>0.7567775858524824</v>
+        <v>0.5464854778016258</v>
       </c>
       <c r="I71" t="n">
-        <v>0.7391160517242967</v>
+        <v>0.6787278164564581</v>
       </c>
     </row>
     <row r="72">
@@ -2500,26 +2500,26 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-0.01981652066781661</v>
+        <v>-0.07532208023287773</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.01465005395010278</v>
+        <v>-0.07493762284906469</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.04607991194050631</v>
+        <v>-0.08694371828258984</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4533815627393399</v>
+        <v>0.4375730194308136</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4548605274836972</v>
+        <v>0.4169779840183686</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4311685280122619</v>
+        <v>0.4574013736501991</v>
       </c>
     </row>
     <row r="73">
@@ -2529,26 +2529,26 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-0.03335378028479172</v>
+        <v>-0.09031125412820135</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.02538458501363067</v>
+        <v>-0.0871907386880576</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.05821926601611788</v>
+        <v>-0.09917315076071936</v>
       </c>
       <c r="G73" t="n">
-        <v>0.431192924270504</v>
+        <v>0.4262875627930028</v>
       </c>
       <c r="H73" t="n">
-        <v>0.4321591439368675</v>
+        <v>0.4080835476445933</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4166809684675389</v>
+        <v>0.4478920171673374</v>
       </c>
     </row>
     <row r="74">
@@ -2558,26 +2558,26 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.2071087641957634</v>
+        <v>0.1938747222045325</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1618118769876409</v>
+        <v>0.1407687891169783</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2500622399012375</v>
+        <v>0.2349141586759712</v>
       </c>
       <c r="G74" t="n">
-        <v>0.825330040329422</v>
+        <v>0.6402532246349539</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8280421738848724</v>
+        <v>0.5735575007598839</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7845956569835802</v>
+        <v>0.7076714736151439</v>
       </c>
     </row>
     <row r="75">
@@ -2587,26 +2587,26 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.1051456769457374</v>
+        <v>0.07655652657305761</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0809590339169412</v>
+        <v>0.04486534232712225</v>
       </c>
       <c r="F75" t="n">
-        <v>0.158628223431727</v>
+        <v>0.1391960782833814</v>
       </c>
       <c r="G75" t="n">
-        <v>0.6582044813780203</v>
+        <v>0.5519235128795724</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6570546020443229</v>
+        <v>0.5039419746596897</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6754748792416655</v>
+        <v>0.633243052677693</v>
       </c>
     </row>
     <row r="76">
@@ -2616,26 +2616,26 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-0.08687883776896865</v>
+        <v>-0.1988491366882734</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.06357314865577374</v>
+        <v>-0.1696232251575539</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.2194559983390776</v>
+        <v>-0.3355396874591366</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3434611245456314</v>
+        <v>0.344568611785726</v>
       </c>
       <c r="H76" t="n">
-        <v>0.3513979793166134</v>
+        <v>0.3482464812470162</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2242550168249871</v>
+        <v>0.2640982342502367</v>
       </c>
     </row>
     <row r="77">
@@ -2645,26 +2645,26 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.1084835514518932</v>
+        <v>0.1994667596414029</v>
       </c>
       <c r="E77" t="n">
-        <v>0.08360584121666652</v>
+        <v>0.1420847284810791</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1616214171531041</v>
+        <v>0.3159349984862588</v>
       </c>
       <c r="G77" t="n">
-        <v>0.6636755215122113</v>
+        <v>0.6444635097681796</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6626520694446235</v>
+        <v>0.5745127303602189</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6790470686676631</v>
+        <v>0.7706716209788672</v>
       </c>
     </row>
     <row r="78">
@@ -2674,26 +2674,26 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.03483392913997907</v>
+        <v>-0.06784707763467634</v>
       </c>
       <c r="E78" t="n">
-        <v>0.02868567039117571</v>
+        <v>-0.06722197887107911</v>
       </c>
       <c r="F78" t="n">
-        <v>0.002927138184791594</v>
+        <v>-0.1185438254119424</v>
       </c>
       <c r="G78" t="n">
-        <v>0.5429579694312729</v>
+        <v>0.443201002552408</v>
       </c>
       <c r="H78" t="n">
-        <v>0.5465069062336348</v>
+        <v>0.4225787067526225</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4896553760256896</v>
+        <v>0.432829776879292</v>
       </c>
     </row>
     <row r="79">
@@ -2703,26 +2703,26 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-0.1524002533028889</v>
+        <v>-0.2711892517850359</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.1155291345994301</v>
+        <v>-0.2287586929476259</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.2782114396326872</v>
+        <v>-0.3945608556178418</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2360663458102447</v>
+        <v>0.2901032197767999</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2415214735353722</v>
+        <v>0.3053205297907816</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1541340738970774</v>
+        <v>0.2182045814532018</v>
       </c>
     </row>
     <row r="80">
@@ -2732,26 +2732,26 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-0.08812456925943375</v>
+        <v>-0.1998809634801799</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.06456096626137273</v>
+        <v>-0.1704667068127338</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.2205730911683332</v>
+        <v>-0.3363815387958992</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3414192721727544</v>
+        <v>0.3437917419862885</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3493089428970156</v>
+        <v>0.3476342048258165</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2229218364284009</v>
+        <v>0.2634436278749069</v>
       </c>
     </row>
     <row r="81">
@@ -2761,26 +2761,26 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-0.2320249002958412</v>
+        <v>0.08064900804388486</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.1786684457120346</v>
+        <v>0.2276389917867627</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.3496137625800115</v>
+        <v>-0.1614280622313669</v>
       </c>
       <c r="G81" t="n">
-        <v>0.105555256023663</v>
+        <v>0.5550047715601776</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1079944745479777</v>
+        <v>0.6366158689803594</v>
       </c>
       <c r="I81" t="n">
-        <v>0.06891986901535771</v>
+        <v>0.3994838717327805</v>
       </c>
     </row>
     <row r="82">
@@ -2790,26 +2790,26 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-0.07019376607936756</v>
+        <v>0.3118848132489208</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.05459729002786502</v>
+        <v>0.4103726602874821</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.09125502394308208</v>
+        <v>0.175045789965036</v>
       </c>
       <c r="G82" t="n">
-        <v>0.370809275797967</v>
+        <v>0.7291038694140539</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3703801228465339</v>
+        <v>0.7692607414505903</v>
       </c>
       <c r="I82" t="n">
-        <v>0.377254858388627</v>
+        <v>0.6611190550022759</v>
       </c>
     </row>
     <row r="83">
@@ -2819,26 +2819,26 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-0.2793148214128824</v>
+        <v>0.05447313837086332</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.2161675512611452</v>
+        <v>0.2062411505494965</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.392020358367511</v>
+        <v>-0.1827845447805754</v>
       </c>
       <c r="G83" t="n">
-        <v>0.02804333761662989</v>
+        <v>0.5352967713585096</v>
       </c>
       <c r="H83" t="n">
-        <v>0.02869137572647791</v>
+        <v>0.6210833513806032</v>
       </c>
       <c r="I83" t="n">
-        <v>0.01831025027174692</v>
+        <v>0.3828775078525571</v>
       </c>
     </row>
     <row r="84">
@@ -2848,26 +2848,26 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-0.07368856912092137</v>
+        <v>0.252031487447482</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.05524115194291382</v>
+        <v>0.365249508403741</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.151008372456617</v>
+        <v>0.03684889936992808</v>
       </c>
       <c r="G84" t="n">
-        <v>0.3650810173909562</v>
+        <v>0.6840398707121881</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3690184838333142</v>
+        <v>0.7365062152804439</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3059429756315692</v>
+        <v>0.5536599803606594</v>
       </c>
     </row>
     <row r="85">
@@ -2877,26 +2877,26 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-0.1421626555078914</v>
+        <v>0.2789066224863308</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.1116658771006392</v>
+        <v>0.3834141638155396</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.1557921500617143</v>
+        <v>0.1481394000599999</v>
       </c>
       <c r="G85" t="n">
-        <v>0.252846577754508</v>
+        <v>0.7042743528280346</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2496914895054406</v>
+        <v>0.7496917897853099</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3002338363749925</v>
+        <v>0.6401971967123321</v>
       </c>
     </row>
     <row r="86">
@@ -2906,26 +2906,26 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-0.01085019507623672</v>
+        <v>0.4381475203280574</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.0110212727840924</v>
+        <v>0.5092355397148202</v>
       </c>
       <c r="F86" t="n">
-        <v>0.05461049742030014</v>
+        <v>0.3802859747002877</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4680780790635126</v>
+        <v>0.8241679680538575</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4625346729651897</v>
+        <v>0.8410244954499113</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5513362315087701</v>
+        <v>0.8207096234727453</v>
       </c>
     </row>
     <row r="87">
@@ -2935,26 +2935,26 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-0.2572060400176483</v>
+        <v>0.06459221769586326</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.1986361300297543</v>
+        <v>0.2145131375194966</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.3721946083168511</v>
+        <v>-0.1745285462705754</v>
       </c>
       <c r="G87" t="n">
-        <v>0.06428137775513999</v>
+        <v>0.542915498830374</v>
       </c>
       <c r="H87" t="n">
-        <v>0.06576682086139013</v>
+        <v>0.627087918933554</v>
       </c>
       <c r="I87" t="n">
-        <v>0.04197104248430625</v>
+        <v>0.3892972033775922</v>
       </c>
     </row>
     <row r="88">
@@ -2964,26 +2964,26 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-0.2826832358164801</v>
+        <v>0.05316242015503597</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.2188385755358746</v>
+        <v>0.2051696850876261</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.3950409383279771</v>
+        <v>-0.1838539392669064</v>
       </c>
       <c r="G88" t="n">
-        <v>0.02252224017672205</v>
+        <v>0.5343099222037524</v>
       </c>
       <c r="H88" t="n">
-        <v>0.02304269427363418</v>
+        <v>0.6203055833824442</v>
       </c>
       <c r="I88" t="n">
-        <v>0.01470537708291991</v>
+        <v>0.3820459685796175</v>
       </c>
     </row>
     <row r="89">
@@ -2993,26 +2993,26 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-0.1255510729092672</v>
+        <v>0.1928422750764388</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.09636614132039685</v>
+        <v>0.3168644352392087</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.1975153697771836</v>
+        <v>-0.01144265299848923</v>
       </c>
       <c r="G89" t="n">
-        <v>0.2800742745783087</v>
+        <v>0.6394758877799476</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2820473668192174</v>
+        <v>0.7013838871838736</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2504397842153457</v>
+        <v>0.5161094572760179</v>
       </c>
     </row>
     <row r="90">
@@ -3022,26 +3022,26 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.2906186651420429</v>
+        <v>0.07285815133158269</v>
       </c>
       <c r="E90" t="n">
-        <v>0.2248409708440215</v>
+        <v>-0.0761449160395683</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4098777585525388</v>
+        <v>0.3050776081694965</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9622093684278324</v>
+        <v>0.54913897960846</v>
       </c>
       <c r="H90" t="n">
-        <v>0.9613360854470026</v>
+        <v>0.416101619785097</v>
       </c>
       <c r="I90" t="n">
-        <v>0.9753254790326068</v>
+        <v>0.7622291364089326</v>
       </c>
     </row>
     <row r="91">
@@ -3051,26 +3051,26 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.2049261313749239</v>
+        <v>0.02027330491683454</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1600811323259815</v>
+        <v>-0.1167225710376978</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2481049935028604</v>
+        <v>0.2056040896556835</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8217525326253449</v>
+        <v>0.5095474712195468</v>
       </c>
       <c r="H91" t="n">
-        <v>0.8243819955171884</v>
+        <v>0.3866466325540672</v>
       </c>
       <c r="I91" t="n">
-        <v>0.7822598058696275</v>
+        <v>0.684880563624051</v>
       </c>
     </row>
     <row r="92">
@@ -3080,26 +3080,26 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-0.2138314577416843</v>
+        <v>-0.582776824492338</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.1663691227285002</v>
+        <v>-0.5982820255941727</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.2766796083109662</v>
+        <v>-0.5544613761216547</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1353757463414756</v>
+        <v>0.05550669929970655</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1340050796469013</v>
+        <v>0.03708657085024292</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1559622187347414</v>
+        <v>0.09386920824719423</v>
       </c>
     </row>
     <row r="93">
@@ -3109,26 +3109,26 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.2794929130106866</v>
+        <v>0.05956934584687051</v>
       </c>
       <c r="E93" t="n">
-        <v>0.2160186733304689</v>
+        <v>-0.08700804125935252</v>
       </c>
       <c r="F93" t="n">
-        <v>0.399900891128746</v>
+        <v>0.2942354796756116</v>
       </c>
       <c r="G93" t="n">
-        <v>0.9439733813284208</v>
+        <v>0.5391337425544813</v>
       </c>
       <c r="H93" t="n">
-        <v>0.9426786929224352</v>
+        <v>0.4082161662108928</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9634187120026877</v>
+        <v>0.7537985191202133</v>
       </c>
     </row>
     <row r="94">
@@ -3138,26 +3138,26 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-0.02901448887185798</v>
+        <v>-0.3752461219480935</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.02194369226400598</v>
+        <v>-0.4324378775658275</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.05432806525693248</v>
+        <v>-0.2957768242294244</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4383053658647966</v>
+        <v>0.2117580551738411</v>
       </c>
       <c r="H94" t="n">
-        <v>0.4394359430434568</v>
+        <v>0.1574714788184609</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4213248731059601</v>
+        <v>0.2950170231561665</v>
       </c>
     </row>
     <row r="95">
@@ -3167,26 +3167,26 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-0.1932859018417178</v>
+        <v>-0.6094640464961151</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.1479498960172134</v>
+        <v>-0.6176093224250361</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.3148750907900814</v>
+        <v>-0.6346837409430216</v>
       </c>
       <c r="G95" t="n">
-        <v>0.169051536339177</v>
+        <v>0.03541369825705265</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1729580555835614</v>
+        <v>0.02305704446707348</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1103783002404843</v>
+        <v>0.03148993869819171</v>
       </c>
     </row>
     <row r="96">
@@ -3196,26 +3196,26 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-0.1505237492145931</v>
+        <v>-0.5584959186585251</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.1140411383581975</v>
+        <v>-0.5759446930830935</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.2765287100259068</v>
+        <v>-0.5930996428279856</v>
       </c>
       <c r="G96" t="n">
-        <v>0.2391420843259098</v>
+        <v>0.07378796762228937</v>
       </c>
       <c r="H96" t="n">
-        <v>0.2446682876056424</v>
+        <v>0.05330105746656988</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1561423063964388</v>
+        <v>0.06382488258878996</v>
       </c>
     </row>
     <row r="97">
@@ -3225,26 +3225,26 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.2536842596471849</v>
+        <v>0.02897042708068348</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1955533946051549</v>
+        <v>-0.1120215676089928</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3767573310391245</v>
+        <v>0.2692703005691367</v>
       </c>
       <c r="G97" t="n">
-        <v>0.901670958603798</v>
+        <v>0.5160955969361003</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8993987267099719</v>
+        <v>0.3900590524184461</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9357983210999391</v>
+        <v>0.7343861066303843</v>
       </c>
     </row>
     <row r="98">
@@ -3254,26 +3254,26 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.3115079062306708</v>
+        <v>0.09630855829866919</v>
       </c>
       <c r="E98" t="n">
-        <v>0.241405343080646</v>
+        <v>-0.05697504350050364</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4286099023630694</v>
+        <v>0.324210428336331</v>
       </c>
       <c r="G98" t="n">
-        <v>0.9964484856139064</v>
+        <v>0.5667949593718704</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9963664156151921</v>
+        <v>0.4300168731649349</v>
       </c>
       <c r="I98" t="n">
-        <v>0.997681120623175</v>
+        <v>0.7771064259163804</v>
       </c>
     </row>
     <row r="99">
@@ -3283,26 +3283,26 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-0.174069862489954</v>
+        <v>-0.6430955085185971</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.1348396927373736</v>
+        <v>-0.6454904172599281</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.2410239367032022</v>
+        <v>-0.6529967337318704</v>
       </c>
       <c r="G99" t="n">
-        <v>0.200548143632174</v>
+        <v>0.01009232904941964</v>
       </c>
       <c r="H99" t="n">
-        <v>0.2006835101256562</v>
+        <v>0.002818386210781175</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1985150318668971</v>
+        <v>0.01725013018633546</v>
       </c>
     </row>
     <row r="100">
@@ -3312,26 +3312,26 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-0.1357099488004962</v>
+        <v>-0.6162624179220144</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.1044217428165946</v>
+        <v>-0.623555321323741</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.206625204037818</v>
+        <v>-0.6311040349132373</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2634230740563361</v>
+        <v>0.03029515560283368</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2650113828360011</v>
+        <v>0.01874089259370512</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2395677670164529</v>
+        <v>0.03427344486676866</v>
       </c>
     </row>
     <row r="101">
@@ -3341,26 +3341,26 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-0.06639082216579527</v>
+        <v>-0.441343533445036</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.05158170040868493</v>
+        <v>-0.4855791695044604</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.08784478553421998</v>
+        <v>-0.3706312836791367</v>
       </c>
       <c r="G101" t="n">
-        <v>0.3770426014490244</v>
+        <v>0.1619928395235639</v>
       </c>
       <c r="H101" t="n">
-        <v>0.3767574910016685</v>
+        <v>0.1188966504907763</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3813247645551626</v>
+        <v>0.2368117269977215</v>
       </c>
     </row>
     <row r="102">
@@ -3370,26 +3370,26 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.1850129948636116</v>
+        <v>-0.117010431712482</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1442907738264732</v>
+        <v>-0.225691784458633</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2302481582417794</v>
+        <v>0.01713805276841723</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7891133279907501</v>
+        <v>0.4061855603079547</v>
       </c>
       <c r="H102" t="n">
-        <v>0.7909885494022286</v>
+        <v>0.3075467735297603</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7609487902658433</v>
+        <v>0.538333229323931</v>
       </c>
     </row>
     <row r="103">
@@ -3399,26 +3399,26 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.09497141375117303</v>
+        <v>-0.2235929788770503</v>
       </c>
       <c r="E103" t="n">
-        <v>0.07289123087550374</v>
+        <v>-0.3128192209633095</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1495045908153882</v>
+        <v>-0.06982097999741005</v>
       </c>
       <c r="G103" t="n">
-        <v>0.6415280598497008</v>
+        <v>0.3259387953579242</v>
       </c>
       <c r="H103" t="n">
-        <v>0.639992814236355</v>
+        <v>0.2443016813765566</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6645863945685856</v>
+        <v>0.4707156646124094</v>
       </c>
     </row>
     <row r="104">
@@ -3428,26 +3428,26 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-0.1234983045398911</v>
+        <v>-0.4405293351356835</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.09686575795426833</v>
+        <v>-0.4858045793677699</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.1390551463103844</v>
+        <v>-0.3490403765244605</v>
       </c>
       <c r="G104" t="n">
-        <v>0.2834389241822236</v>
+        <v>0.1626058552760626</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2809907776897278</v>
+        <v>0.118733027318224</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3202084031383751</v>
+        <v>0.2536003746548686</v>
       </c>
     </row>
     <row r="105">
@@ -3457,26 +3457,26 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.05251978634480212</v>
+        <v>-0.2585557795191367</v>
       </c>
       <c r="E105" t="n">
-        <v>0.03922870788454512</v>
+        <v>-0.3414000653323741</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1114366693340224</v>
+        <v>-0.09834658205424462</v>
       </c>
       <c r="G105" t="n">
-        <v>0.5719464872430458</v>
+        <v>0.2996150517454899</v>
       </c>
       <c r="H105" t="n">
-        <v>0.568803319227285</v>
+        <v>0.2235550806678253</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6191547121438068</v>
+        <v>0.4485347400820354</v>
       </c>
     </row>
     <row r="106">
@@ -3486,26 +3486,26 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.2022951084233028</v>
+        <v>-0.1008388465196763</v>
       </c>
       <c r="E106" t="n">
-        <v>0.1579948313757053</v>
+        <v>-0.2124720894940287</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2457456593322474</v>
+        <v>0.03033219612553956</v>
       </c>
       <c r="G106" t="n">
-        <v>0.8174400780571007</v>
+        <v>0.4183612629005447</v>
       </c>
       <c r="H106" t="n">
-        <v>0.8199698868013028</v>
+        <v>0.317142841769743</v>
       </c>
       <c r="I106" t="n">
-        <v>0.779444088157651</v>
+        <v>0.5485927252484752</v>
       </c>
     </row>
     <row r="107">
@@ -3515,26 +3515,26 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.06955503646431022</v>
+        <v>-0.2459908736383813</v>
       </c>
       <c r="E107" t="n">
-        <v>0.05273701213199576</v>
+        <v>-0.3311287022580576</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1267127989805277</v>
+        <v>-0.08809507192194244</v>
       </c>
       <c r="G107" t="n">
-        <v>0.5998686086193677</v>
+        <v>0.3090752595905453</v>
       </c>
       <c r="H107" t="n">
-        <v>0.5973706775938333</v>
+        <v>0.2310109789500994</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6373858170681852</v>
+        <v>0.4565061046167403</v>
       </c>
     </row>
     <row r="108">
@@ -3544,26 +3544,26 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.2574736758381928</v>
+        <v>0.03335853824021584</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1985582572557908</v>
+        <v>-0.1084344430130936</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3801554386461335</v>
+        <v>0.2728504918129496</v>
       </c>
       <c r="G108" t="n">
-        <v>0.9078821112483697</v>
+        <v>0.5193994373317505</v>
       </c>
       <c r="H108" t="n">
-        <v>0.9057534094747735</v>
+        <v>0.3926629167662797</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9398537499134725</v>
+        <v>0.7371699900914626</v>
       </c>
     </row>
     <row r="109">
@@ -3573,26 +3573,26 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>-0.01085019507623672</v>
+        <v>-0.2853079988360432</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.0110212727840924</v>
+        <v>-0.363269051877554</v>
       </c>
       <c r="F109" t="n">
-        <v>0.05461049742030014</v>
+        <v>-0.1201732992610072</v>
       </c>
       <c r="G109" t="n">
-        <v>0.4680780790635126</v>
+        <v>0.2794731137591446</v>
       </c>
       <c r="H109" t="n">
-        <v>0.4625346729651897</v>
+        <v>0.2076805625500698</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5513362315087701</v>
+        <v>0.43156273135302</v>
       </c>
     </row>
     <row r="110">
@@ -3602,26 +3602,26 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.1056991107935018</v>
+        <v>-0.2123054582919784</v>
       </c>
       <c r="E110" t="n">
-        <v>0.08139788587062502</v>
+        <v>-0.3035920748757555</v>
       </c>
       <c r="F110" t="n">
-        <v>0.15912450773339</v>
+        <v>-0.06061166854338129</v>
       </c>
       <c r="G110" t="n">
-        <v>0.6591116031967571</v>
+        <v>0.3344372506431064</v>
       </c>
       <c r="H110" t="n">
-        <v>0.6579826860436975</v>
+        <v>0.2509995911054524</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6760671635037991</v>
+        <v>0.4778766367780986</v>
       </c>
     </row>
     <row r="111">
@@ -3631,26 +3631,26 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.1109428107855976</v>
+        <v>-0.08711386761014395</v>
       </c>
       <c r="E111" t="n">
-        <v>0.08555594016267606</v>
+        <v>-0.2045077601204317</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1638267246274585</v>
+        <v>0.1179885756448919</v>
       </c>
       <c r="G111" t="n">
-        <v>0.6677064419348537</v>
+        <v>0.4286948980574976</v>
       </c>
       <c r="H111" t="n">
-        <v>0.6667761381967318</v>
+        <v>0.3229240831947053</v>
       </c>
       <c r="I111" t="n">
-        <v>0.6816789651549168</v>
+        <v>0.6167525325279408</v>
       </c>
     </row>
     <row r="112">
@@ -3660,26 +3660,26 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.1909844985770585</v>
+        <v>0.008039164495971196</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1490259487379146</v>
+        <v>-0.1267235451283453</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2356030232582161</v>
+        <v>0.1956224458873382</v>
       </c>
       <c r="G112" t="n">
-        <v>0.7989010945522214</v>
+        <v>0.500336299063914</v>
       </c>
       <c r="H112" t="n">
-        <v>0.8010024960934991</v>
+        <v>0.3793870074192126</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7673394866156137</v>
+        <v>0.6771190416525384</v>
       </c>
     </row>
     <row r="113">
@@ -3689,26 +3689,26 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-0.104721360630777</v>
+        <v>-0.03083100196658278</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.08197635689574416</v>
+        <v>0.007235155417122274</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.1222171763652111</v>
+        <v>-0.06542072527730219</v>
       </c>
       <c r="G113" t="n">
-        <v>0.3142158193395346</v>
+        <v>0.4710706716730341</v>
       </c>
       <c r="H113" t="n">
-        <v>0.312478879238995</v>
+        <v>0.4766265303594607</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3403034667367786</v>
+        <v>0.4741372126542937</v>
       </c>
     </row>
     <row r="114">
@@ -3718,26 +3718,26 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.2043501191762916</v>
+        <v>0.3749854758686689</v>
       </c>
       <c r="E114" t="n">
-        <v>0.1564333009997117</v>
+        <v>0.3289593501938129</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3325176092536931</v>
+        <v>0.5009317564038488</v>
       </c>
       <c r="G114" t="n">
-        <v>0.82080840310499</v>
+        <v>0.7766128113200832</v>
       </c>
       <c r="H114" t="n">
-        <v>0.8166675627616531</v>
+        <v>0.7101634868321204</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8830009811742454</v>
+        <v>0.914521314933031</v>
       </c>
     </row>
     <row r="115">
@@ -3747,26 +3747,26 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>-0.01085019507623672</v>
+        <v>0.2355507258907915</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.0110212727840924</v>
+        <v>0.2173849920820863</v>
       </c>
       <c r="F115" t="n">
-        <v>0.05461049742030014</v>
+        <v>0.3305987603247842</v>
       </c>
       <c r="G115" t="n">
-        <v>0.4680780790635126</v>
+        <v>0.6716313870155544</v>
       </c>
       <c r="H115" t="n">
-        <v>0.4625346729651897</v>
+        <v>0.629172574625815</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5513362315087701</v>
+        <v>0.7820738621664035</v>
       </c>
     </row>
     <row r="116">
@@ -3776,26 +3776,26 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-0.2012959215250065</v>
+        <v>-0.2156926003032733</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.1543015364187842</v>
+        <v>-0.1375892505273381</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.322057967372143</v>
+        <v>-0.3640585876063669</v>
       </c>
       <c r="G116" t="n">
-        <v>0.1559224809831072</v>
+        <v>0.3318870471054383</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1595256080873211</v>
+        <v>0.3714996809140653</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1018059864635857</v>
+        <v>0.2419225209876511</v>
       </c>
     </row>
     <row r="117">
@@ -3805,26 +3805,26 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.1118735812726181</v>
+        <v>0.3157567381758632</v>
       </c>
       <c r="E117" t="n">
-        <v>0.08629400569356152</v>
+        <v>0.2829505506896401</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1646613804459007</v>
+        <v>0.3960375909388129</v>
       </c>
       <c r="G117" t="n">
-        <v>0.669232048329228</v>
+        <v>0.7320190694893229</v>
       </c>
       <c r="H117" t="n">
-        <v>0.6683369989926219</v>
+        <v>0.676766076312146</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6826750746508351</v>
+        <v>0.8329577579844033</v>
       </c>
     </row>
     <row r="118">
@@ -3834,26 +3834,26 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-0.004933646450426488</v>
+        <v>0.2360410853319784</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.006329675163183043</v>
+        <v>0.2177858434617265</v>
       </c>
       <c r="F118" t="n">
-        <v>0.05991608220676758</v>
+        <v>0.3309988369212588</v>
       </c>
       <c r="G118" t="n">
-        <v>0.4777757698928125</v>
+        <v>0.6720005821592696</v>
       </c>
       <c r="H118" t="n">
-        <v>0.472456462413592</v>
+        <v>0.6294635493573362</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5576681149874758</v>
+        <v>0.7823849535423222</v>
       </c>
     </row>
     <row r="119">
@@ -3863,26 +3863,26 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-0.2269547785120792</v>
+        <v>-0.2372986627297122</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.1746480323253093</v>
+        <v>-0.1552514370884173</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.345067199591563</v>
+        <v>-0.3816866359169424</v>
       </c>
       <c r="G119" t="n">
-        <v>0.113865586359043</v>
+        <v>0.3156196875878144</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1164968437496429</v>
+        <v>0.3586788444302263</v>
       </c>
       <c r="I119" t="n">
-        <v>0.07434590746919228</v>
+        <v>0.2282153112882513</v>
       </c>
     </row>
     <row r="120">
@@ -3892,26 +3892,26 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-0.2189492958767946</v>
+        <v>-0.2311204265252159</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.1682999896299297</v>
+        <v>-0.150200949021295</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.3378883915458031</v>
+        <v>-0.3766459096551439</v>
       </c>
       <c r="G120" t="n">
-        <v>0.1269872051348353</v>
+        <v>0.3202713259816921</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1299216828177505</v>
+        <v>0.362344952329621</v>
       </c>
       <c r="I120" t="n">
-        <v>0.08291336570257801</v>
+        <v>0.2321348768970143</v>
       </c>
     </row>
     <row r="121">
@@ -3921,26 +3921,26 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-0.01085019507623672</v>
+        <v>0.3056079890815467</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.0110212727840924</v>
+        <v>0.3069648770159712</v>
       </c>
       <c r="F121" t="n">
-        <v>0.05461049742030014</v>
+        <v>0.3770964331285971</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4680780790635126</v>
+        <v>0.7243780034351314</v>
       </c>
       <c r="H121" t="n">
-        <v>0.4625346729651897</v>
+        <v>0.6941978789960731</v>
       </c>
       <c r="I121" t="n">
-        <v>0.5513362315087701</v>
+        <v>0.8182295012040828</v>
       </c>
     </row>
     <row r="122">
@@ -3950,26 +3950,26 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-0.1107366680673225</v>
+        <v>0.03646404584935259</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.08674626649054114</v>
+        <v>0.0945570276548921</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.1276113217766146</v>
+        <v>-0.02117670078341721</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3043562550137504</v>
+        <v>0.5217375963060912</v>
       </c>
       <c r="H122" t="n">
-        <v>0.3023914756482505</v>
+        <v>0.5400127618179246</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3338658916933416</v>
+        <v>0.5085404608754385</v>
       </c>
     </row>
     <row r="123">
@@ -3979,26 +3979,26 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-0.2142462869037103</v>
+        <v>-0.1110517355042445</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.1666980664476738</v>
+        <v>-0.02222705965546756</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.2770516007393606</v>
+        <v>-0.2308960173993885</v>
       </c>
       <c r="G123" t="n">
-        <v>0.134695808557688</v>
+        <v>0.410671905462502</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1333094295537499</v>
+        <v>0.455240149879835</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1555182690465634</v>
+        <v>0.3454670110968064</v>
       </c>
     </row>
     <row r="124">
@@ -4008,26 +4008,26 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-0.09342398599277174</v>
+        <v>0.04498142015294965</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.07301796927378336</v>
+        <v>0.1015196778125899</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.1120864087847764</v>
+        <v>-0.01422750834197845</v>
       </c>
       <c r="G124" t="n">
-        <v>0.3327331092920272</v>
+        <v>0.5281503885681943</v>
       </c>
       <c r="H124" t="n">
-        <v>0.3314240750900066</v>
+        <v>0.5450668925087832</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3523939039743055</v>
+        <v>0.5139440107385926</v>
       </c>
     </row>
     <row r="125">
@@ -4037,26 +4037,26 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.1157128921277209</v>
+        <v>0.3942641269346043</v>
       </c>
       <c r="E125" t="n">
-        <v>0.08614735731102405</v>
+        <v>0.3770295281315827</v>
       </c>
       <c r="F125" t="n">
-        <v>0.253033377299264</v>
+        <v>0.5059999539977336</v>
       </c>
       <c r="G125" t="n">
-        <v>0.6755249822718208</v>
+        <v>0.7911278461151614</v>
       </c>
       <c r="H125" t="n">
-        <v>0.6680268670307501</v>
+        <v>0.7450572350641365</v>
       </c>
       <c r="I125" t="n">
-        <v>0.7881415235676963</v>
+        <v>0.9184622416875654</v>
       </c>
     </row>
     <row r="126">
@@ -4066,26 +4066,26 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>-0.02228142138431866</v>
+        <v>0.1040891491991728</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.0166046262977162</v>
+        <v>0.1498381412610072</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.04829027824842036</v>
+        <v>0.03399756305651086</v>
       </c>
       <c r="G126" t="n">
-        <v>0.4493413956444091</v>
+        <v>0.5726530221201833</v>
       </c>
       <c r="H126" t="n">
-        <v>0.4507269983830215</v>
+        <v>0.5801408691582893</v>
       </c>
       <c r="I126" t="n">
-        <v>0.4285305941236797</v>
+        <v>0.5514428395812077</v>
       </c>
     </row>
     <row r="127">
@@ -4095,26 +4095,26 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>-0.1031563085897094</v>
+        <v>0.03998083156589932</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.0807353302606479</v>
+        <v>0.09743187473230219</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.120813737160318</v>
+        <v>-0.0183074103367985</v>
       </c>
       <c r="G127" t="n">
-        <v>0.3167810633332761</v>
+        <v>0.5243854095201965</v>
       </c>
       <c r="H127" t="n">
-        <v>0.3151034020493927</v>
+        <v>0.5420995897521701</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3419783836163461</v>
+        <v>0.5107715624215292</v>
       </c>
     </row>
     <row r="128">
@@ -4124,26 +4124,26 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>-0.1190679721918321</v>
+        <v>0.03298816443658287</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.09335267321203905</v>
+        <v>0.09171561838906472</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.1350823058266069</v>
+        <v>-0.02401261804852517</v>
       </c>
       <c r="G128" t="n">
-        <v>0.2907005890648711</v>
+        <v>0.5191205802359645</v>
       </c>
       <c r="H128" t="n">
-        <v>0.2884202484038078</v>
+        <v>0.5379502061170854</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3249497396799993</v>
+        <v>0.5063353096324809</v>
       </c>
     </row>
     <row r="129">
@@ -4153,26 +4153,26 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.02292399772415807</v>
+        <v>-0.2949721968890288</v>
       </c>
       <c r="E129" t="n">
-        <v>0.01924154858477241</v>
+        <v>-0.3601303435318705</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.007752931383469164</v>
+        <v>-0.2324040815009353</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5234366505047372</v>
+        <v>0.2721968696627163</v>
       </c>
       <c r="H129" t="n">
-        <v>0.5265344798536343</v>
+        <v>0.2099589252166235</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4769093812348452</v>
+        <v>0.3442943713061815</v>
       </c>
     </row>
     <row r="130">
@@ -4182,26 +4182,26 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.002403966238747918</v>
+        <v>-0.3192629675188849</v>
       </c>
       <c r="E130" t="n">
-        <v>0.002969945495437151</v>
+        <v>-0.3799871834367625</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.02615399148663297</v>
+        <v>-0.2522225412328776</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4898026970398899</v>
+        <v>0.2539081740643701</v>
       </c>
       <c r="H130" t="n">
-        <v>0.4921232978032299</v>
+        <v>0.1955450078555991</v>
       </c>
       <c r="I130" t="n">
-        <v>0.454948867333517</v>
+        <v>0.3288839425009762</v>
       </c>
     </row>
     <row r="131">
@@ -4211,17 +4211,17 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-0.2964240254037444</v>
+        <v>-0.6564999882827337</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.2297344981107014</v>
+        <v>-0.6493730705578418</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.4073628051457719</v>
+        <v>-0.6751811268328057</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4240,26 +4240,26 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.1062791308560538</v>
+        <v>-0.1938805140377699</v>
       </c>
       <c r="E132" t="n">
-        <v>0.08185781967961582</v>
+        <v>-0.2818438799766907</v>
       </c>
       <c r="F132" t="n">
-        <v>0.1596446328628102</v>
+        <v>-0.04770054163683451</v>
       </c>
       <c r="G132" t="n">
-        <v>0.6600623019228491</v>
+        <v>0.3483095234506041</v>
       </c>
       <c r="H132" t="n">
-        <v>0.658955353945282</v>
+        <v>0.2667864275571751</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6766879003021697</v>
+        <v>0.4879160649011443</v>
       </c>
     </row>
     <row r="133">
@@ -4269,26 +4269,26 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.1461264108531443</v>
+        <v>-0.04875022679316537</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1102641188082963</v>
+        <v>-0.1688689750759713</v>
       </c>
       <c r="F133" t="n">
-        <v>0.2803062879871994</v>
+        <v>0.2037377381444604</v>
       </c>
       <c r="G133" t="n">
-        <v>0.7253751432835354</v>
+        <v>0.4575791586533158</v>
       </c>
       <c r="H133" t="n">
-        <v>0.7190289880751568</v>
+        <v>0.3487939852001906</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8206900360411221</v>
+        <v>0.6834293268741619</v>
       </c>
     </row>
     <row r="134">
@@ -4298,26 +4298,26 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>-0.1636632635569094</v>
+        <v>-0.5561310518199639</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.1244602725742835</v>
+        <v>-0.5673250395120144</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.2883113914175632</v>
+        <v>-0.5932916818276978</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2176053817991921</v>
+        <v>0.07556849284316931</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2226339052310917</v>
+        <v>0.05955799335613122</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1420804133834432</v>
+        <v>0.06367555699169938</v>
       </c>
     </row>
     <row r="135">
@@ -4327,26 +4327,26 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-0.2084421996905251</v>
+        <v>-0.606288138521223</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.1599682627080679</v>
+        <v>-0.6083266716092087</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.3284662954554177</v>
+        <v>-0.6342140641682014</v>
       </c>
       <c r="G135" t="n">
-        <v>0.1442091662429812</v>
+        <v>0.03780486217219706</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1475416167805176</v>
+        <v>0.0297952446233641</v>
       </c>
       <c r="I135" t="n">
-        <v>0.09415804785743828</v>
+        <v>0.03185514974878411</v>
       </c>
     </row>
     <row r="136">
@@ -4356,26 +4356,26 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-0.209758956671637</v>
+        <v>-0.2390316589194604</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.1610124008214522</v>
+        <v>-0.1645323248484173</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.3296470794307215</v>
+        <v>-0.3804667761002157</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1420508974772281</v>
+        <v>0.3143149023148251</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1453334737654644</v>
+        <v>0.3519419240617125</v>
       </c>
       <c r="I136" t="n">
-        <v>0.09274885606312068</v>
+        <v>0.2291638493236113</v>
       </c>
     </row>
     <row r="137">
@@ -4385,26 +4385,26 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-0.2168812703508505</v>
+        <v>-0.2450111987340288</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.1666601241862192</v>
+        <v>-0.1694203856930936</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.3360339176857202</v>
+        <v>-0.3853453890860432</v>
       </c>
       <c r="G137" t="n">
-        <v>0.1303768624242588</v>
+        <v>0.3098128638594284</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1333896698385669</v>
+        <v>0.3483937207520074</v>
       </c>
       <c r="I137" t="n">
-        <v>0.08512656422242842</v>
+        <v>0.225370339681433</v>
       </c>
     </row>
     <row r="138">
@@ -4414,26 +4414,26 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-0.009341886089686807</v>
+        <v>0.03478032627370503</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.006344067846604962</v>
+        <v>0.05300585449589923</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.03668692535723098</v>
+        <v>-0.009255684748561199</v>
       </c>
       <c r="G138" t="n">
-        <v>0.4705503167060474</v>
+        <v>0.5204699117496306</v>
       </c>
       <c r="H138" t="n">
-        <v>0.4724260247703735</v>
+        <v>0.5098511057318629</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4423784697917326</v>
+        <v>0.5178099990421593</v>
       </c>
     </row>
     <row r="139">
@@ -4443,26 +4443,26 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.1965974084554652</v>
+        <v>0.3527535983576978</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1502856968010819</v>
+        <v>0.3029213569953957</v>
       </c>
       <c r="F139" t="n">
-        <v>0.3255654709961178</v>
+        <v>0.4854268996520862</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8081010974755569</v>
+        <v>0.7598742711323906</v>
       </c>
       <c r="H139" t="n">
-        <v>0.8036666109751919</v>
+        <v>0.6912627209496075</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8747040391506069</v>
+        <v>0.902465055549622</v>
       </c>
     </row>
     <row r="140">
@@ -4472,26 +4472,26 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-0.1873920249897645</v>
+        <v>-0.1867261104084892</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.1454036599828757</v>
+        <v>-0.1242629584621583</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.2529704053544529</v>
+        <v>-0.2793428194759713</v>
       </c>
       <c r="G140" t="n">
-        <v>0.1787120663391958</v>
+        <v>0.3536961253068167</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1783428348975505</v>
+        <v>0.3811731271157972</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1842576690075439</v>
+        <v>0.3077957690154783</v>
       </c>
     </row>
     <row r="141">
@@ -4501,26 +4501,26 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.1095195603194468</v>
+        <v>0.3081247473580577</v>
       </c>
       <c r="E141" t="n">
-        <v>0.08123628117274212</v>
+        <v>0.2664388607031654</v>
       </c>
       <c r="F141" t="n">
-        <v>0.24747959094548</v>
+        <v>0.4490149183322301</v>
       </c>
       <c r="G141" t="n">
-        <v>0.6653736219301002</v>
+        <v>0.7262728888101203</v>
       </c>
       <c r="H141" t="n">
-        <v>0.6576409244699597</v>
+        <v>0.664780375863543</v>
       </c>
       <c r="I141" t="n">
-        <v>0.7815134270480664</v>
+        <v>0.8741518438583159</v>
       </c>
     </row>
   </sheetData>
